--- a/AAII_Financials/Yearly/LNVGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LNVGY_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>83074600</v>
+      </c>
+      <c r="E8" s="3">
         <v>69077000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>56863800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>61946900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71618200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>60742300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>50716300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>51037900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45349900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>43034700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>44912100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46295600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>38707100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>33873400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29574400</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>70265100</v>
+      </c>
+      <c r="E9" s="3">
         <v>57979400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>47060600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>51445800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>59569200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>50974400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>42359000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43667300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39077800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36929200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>38288200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>39613800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33643500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29799500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26128200</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12809400</v>
+      </c>
+      <c r="E10" s="3">
         <v>11097600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9803200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10501100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12049000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9767900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8357300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7370600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6272100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6105500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6623900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6681800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5063600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4073900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3446200</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2490400</v>
+      </c>
+      <c r="E12" s="3">
         <v>2288200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2027500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2195300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2073500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1453900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1335700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1266300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1273700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1254300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1398600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1163600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>704900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>617300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>449900</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,41 +998,44 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3600</v>
+        <v>4700</v>
       </c>
       <c r="E14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>2300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-110000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>49800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>10</v>
@@ -1030,57 +1049,63 @@
       <c r="Q14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1077900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1052800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1033800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>964400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>909300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>769400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>714200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>666500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>643400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>433000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>432100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>287900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>127200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>92300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>71200</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>67070100</v>
+        <v>79493100</v>
       </c>
       <c r="E17" s="3">
+        <v>67069500</v>
+      </c>
+      <c r="F17" s="3">
         <v>54873000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>59502600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>68646900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>58300600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49316000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>49988000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>44635600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42362400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>44973900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>45187100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37655100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33073400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28990400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2006900</v>
+        <v>3581500</v>
       </c>
       <c r="E18" s="3">
+        <v>2007400</v>
+      </c>
+      <c r="F18" s="3">
         <v>1990800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2444300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2971300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2441800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1400400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1049900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>714400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>672300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-61800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1108500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1052100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>800000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>584100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>703700</v>
+      </c>
+      <c r="E20" s="3">
         <v>338800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>494800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>116800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>545300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>157400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-21700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>356200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>15800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-36400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2720900</v>
+        <v>3955700</v>
       </c>
       <c r="E21" s="3">
+        <v>2721500</v>
+      </c>
+      <c r="F21" s="3">
         <v>2529800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3291800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3881400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2665900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1957200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1738100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1001600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1430200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>642400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1597000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1316300</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>832100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>314100</v>
+      </c>
+      <c r="E22" s="3">
         <v>293600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>275200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>316100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>258600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>267000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>261700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>237400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>187300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>198200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>178600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>117300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7800</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2669900</v>
+      </c>
+      <c r="E23" s="3">
         <v>1480900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1365500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2136000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2767700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1774200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1017700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>856700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>153200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>489900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-276900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>971000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1014200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>801300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>582400</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E24" s="3">
         <v>18900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>263100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>455200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>622400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>461200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>213200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>199500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>280000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-40500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-132300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>134400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>196700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>169700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>107000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2159900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1462000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1102300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1680800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2145300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1313000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>804500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>657200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-126800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>530400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-144600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>836600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>817500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>631600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>475400</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1384500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1010500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1607700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2029800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1135700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>665100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>596300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-189300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>535100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-128100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>828700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>817200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>635100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>473000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-703700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-338800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-494800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-116800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-545300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-157400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>21700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-356200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-15800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>36400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1384400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1010500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1607700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2029800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1210800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>718900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>650100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-135600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>535100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-128100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>828700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>817200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>635100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>473000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1384400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1010500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1607700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2029800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1210800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>718900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>650100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-135600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>535100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-128100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>828700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>817200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>635100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>473000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4887200</v>
+      </c>
+      <c r="E41" s="3">
         <v>4728100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3559800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4250100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3930300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3068400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3551000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2662900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1848000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2754600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1926900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2855200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3858100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3454100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3757700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E42" s="3">
         <v>58200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>60400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>198000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>131600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>30400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>16300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>119300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>88500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>100800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>94200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>119100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>413700</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20638000</v>
+      </c>
+      <c r="E43" s="3">
         <v>13760700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10936700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10236200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15244900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12518900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8850900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9481000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8557600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8062800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7485700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8092500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5622100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3516900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3064600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11720900</v>
+      </c>
+      <c r="E44" s="3">
         <v>7923800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6702700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6371900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8300700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6380600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4946900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3434700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3791700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2794000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2637300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2954400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2701000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1964800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1218500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E45" s="3">
         <v>110800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>127600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>97800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>172100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>164500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>189400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>139600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>98200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1137700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>828300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1504200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1125200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3335000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3365900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39202300</v>
+      </c>
+      <c r="E46" s="3">
         <v>27904100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22687200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22940900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28996900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23335400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18733400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16886200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15663300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14868400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12966800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15507200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13400500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12389700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11820400</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2347100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1825500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1768400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1738400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1508500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>955300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>611300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>599900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>408700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>288500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>180000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>119100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>55900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>72700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>75400</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3518800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2900900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2919100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3303900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2986100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2674900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2514900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1662900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1687600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1649400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1622600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1754900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1019300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>663800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>496500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7920700</v>
+      </c>
+      <c r="E49" s="3">
         <v>8233000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8345400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8267100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8066800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8405000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7984600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8324600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8514500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8349100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8661100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9225700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3339500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3326400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3091200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>378300</v>
+      </c>
+      <c r="E52" s="3">
         <v>311400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>397500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>202500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>424200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>275400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>224400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>652000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>689400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2030600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1502900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>789600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>541800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>429300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>377300</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>57129100</v>
+      </c>
+      <c r="E54" s="3">
         <v>44230800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38751000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>38920100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44510400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37990600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32128200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29988500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28494200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27186000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24933400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27396500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18357100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16882000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15860700</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19236700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11978900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10505400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9772900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13184800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11106400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8968400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7702700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7252800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5649900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4266700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4664100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4751300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3624500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4050300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>988500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1125300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>152000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>395300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>933000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>831900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3387000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1953000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1166700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>905600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>980500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1339300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>554000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>275300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>190300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16004200</v>
+      </c>
+      <c r="E59" s="3">
         <v>12498600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12074400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12361500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14199400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12047400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8562000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8864700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9174800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11778300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10513100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11445000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8156900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8191600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7569100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41357600</v>
+      </c>
+      <c r="E60" s="3">
         <v>29994100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26059200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>26093400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32758700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27371600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23258100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20490300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19459700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18333800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15760300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17448400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13462300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12091500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11809700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4168000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4607600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3809700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3964000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2896300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3632800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1911400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2426800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2648700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2966700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2505100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1885800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>303100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E62" s="3">
         <v>750800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>574400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>642700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1178100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1303000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1181400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1452200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>553300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1790200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3641800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3956100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1859900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1807200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1603100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48685500</v>
+      </c>
+      <c r="E66" s="3">
         <v>37570900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32669800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32873000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39115700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34380100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28068900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25891400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>23948200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>23118700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21933200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>23312900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15347000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14215400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13499500</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7250000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5971600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5207100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4805900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3803200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2204400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1438100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1260700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1088600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1879900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1578600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2110800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1678000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1119400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>731200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7087700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5521600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5035200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5040200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4443300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2792800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2431300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2630200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3305700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4067300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3000200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4083600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3010100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2666600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2361200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1384400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1010500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1607700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2029800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1210800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>718900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>650100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-135600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>535100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-128100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>828700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>817200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>635100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>473000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>640300</v>
+      </c>
+      <c r="E83" s="3">
         <v>569800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>580400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>528700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>481500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>401300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>380100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>289000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>246800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>742100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>740600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>508700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>255100</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>241800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4023700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1099800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2011000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2801400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4077000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3652800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2209900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1472600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-756300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2119800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>292300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>238500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1432100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1940000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1262000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-666500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-729800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1117100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-998300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-697000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-664200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-537700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-503300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-463600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-603800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-606100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-565800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-388400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-306800</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1909100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1056300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1283500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1915000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1498400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-975900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-957000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-699700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1113500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1397600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-853600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3281900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-583700</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-837100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>612500</v>
+      </c>
+      <c r="E96" s="3">
         <v>608400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>583300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>578800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>478800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>434300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>431100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>404400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>380800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-376900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-379400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-326900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-266700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-194700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-114700</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1997400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1189900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1336100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-413800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1757400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3228200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-238500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>122700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>874300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>145100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-305100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2142600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-430100</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-315500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-65100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-81700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-152800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>40700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>68700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-126300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-80700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>88800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-39600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-61800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-102100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-14200</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>15800</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1168300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-690300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>319800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>861900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-482600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>888100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>814800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-906600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>827700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-928300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1002900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>404100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-303600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>803200</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
